--- a/Feuilles/Viser.xlsx
+++ b/Feuilles/Viser.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B571EA-BB63-9245-89E6-3601A29E33DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE486E73-CDB0-624A-B752-AAB7E58CAFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4140" yWindow="1960" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>MES</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>END</t>
+  </si>
+  <si>
+    <t>LOOP</t>
   </si>
 </sst>
 </file>
@@ -449,10 +452,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -465,8 +468,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -480,7 +486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -491,7 +497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -502,7 +508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -513,7 +519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -527,7 +533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -538,7 +544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -549,7 +555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -560,7 +566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -571,7 +577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -582,7 +588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -593,7 +599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -604,7 +610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -615,7 +621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -626,7 +632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>

--- a/Feuilles/Viser.xlsx
+++ b/Feuilles/Viser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE486E73-CDB0-624A-B752-AAB7E58CAFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A07119F-9948-E047-BEF7-7596825CF7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4140" yWindow="1960" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -1001,7 +1001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1014,8 +1014,11 @@
       <c r="D49" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1026,7 +1029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1037,7 +1040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1048,7 +1051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1059,7 +1062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1070,7 +1073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1081,7 +1084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1092,7 +1095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1103,7 +1106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1114,7 +1117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1125,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1147,7 +1150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1158,7 +1161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1169,7 +1172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1180,7 +1183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1193,8 +1196,11 @@
       <c r="D65" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1205,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1216,7 +1222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1227,7 +1233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1238,7 +1244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1249,7 +1255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1260,7 +1266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1271,7 +1277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1282,7 +1288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1293,7 +1299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1304,7 +1310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1315,7 +1321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1326,7 +1332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1337,7 +1343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1348,7 +1354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1359,7 +1365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1372,8 +1378,11 @@
       <c r="D81" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1384,7 +1393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1395,7 +1404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1406,7 +1415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1417,7 +1426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1428,7 +1437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1439,7 +1448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1450,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1461,7 +1470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1472,7 +1481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1483,7 +1492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1494,7 +1503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1505,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1516,7 +1525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1527,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1538,7 +1547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1551,8 +1560,11 @@
       <c r="D97" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1563,7 +1575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1574,7 +1586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1585,7 +1597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1596,7 +1608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1607,7 +1619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -1618,7 +1630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1629,7 +1641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1640,7 +1652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -1651,7 +1663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1662,7 +1674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1673,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1684,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1695,7 +1707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1706,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -1717,7 +1729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -1727,8 +1739,11 @@
       <c r="C113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -1739,7 +1754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -1750,7 +1765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -1761,7 +1776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -1772,7 +1787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -1783,7 +1798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -1794,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -1805,7 +1820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -1816,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -1827,7 +1842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -1838,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -1849,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -1860,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -1871,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -1882,7 +1897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
@@ -1894,6 +1909,9 @@
       </c>
       <c r="D128" t="s">
         <v>12</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
